--- a/EstablecimientoSalud/excels/MOQUEGUA-ILO-ILO.xlsx
+++ b/EstablecimientoSalud/excels/MOQUEGUA-ILO-ILO.xlsx
@@ -741,7 +741,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>21767</t>
+          <t>2817</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -766,22 +766,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-17.66006398</t>
+          <t>-17.634884</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-71.3324777</t>
+          <t>-71.334828</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>POLICLINICO SAN GERONIMO</t>
+          <t>C.S. MIRAMAR</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>OTROS URBANIZACION LOS OLIVARES MZ. 2 LOTE 14 Y 15 PAMPA INALAMBRICA DISTRITO ILO PROVINCIA ILO DEPARTAMENTO MOQUEGUA</t>
+          <t>AVENIDA AVENIDA PACIFICO S/N UPIS MIRAMAR S/N AVENIDA PACIFICO S/N UPIS MIRAMAR ILO ILO MOQUEGUA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -803,7 +803,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2817</t>
+          <t>12046</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -828,32 +828,32 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-17.634884</t>
+          <t>-17.644121</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-71.334828</t>
+          <t>-71.338903</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>C.S. MIRAMAR</t>
+          <t>P.S. JHON F. KENNEDY</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>AVENIDA AVENIDA PACIFICO S/N UPIS MIRAMAR S/N AVENIDA PACIFICO S/N UPIS MIRAMAR ILO ILO MOQUEGUA</t>
+          <t>OTROS JHON F. KENNEDY LOTE 25 MZ. N JHON F. KENNEDY LOTE 25 MZ. N ILO ILO MOQUEGUA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -865,7 +865,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>30305</t>
+          <t>7731</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-17.65055996</t>
+          <t>-17.65531778</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-71.33266009</t>
+          <t>-71.3151922</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>POLICLINICO MANCHEGO SAC</t>
+          <t>P.S. LOS ANGELES - ILO</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>URBANIZACION LUIS E VALCARCEL 61 1 A DOS CUADRAS DE LA MUNICIPALIDAD DEL CENTRO POBLADO PAMPA INALAMBRICA ILO ILO MOQUEGUA</t>
+          <t>OTROS A.H. LOS ANGELES MZ. O LT. 2  PAMPA INALAMBRICA A.H. LOS ANGELES MZ. O LT. 2  PAMPA INALAMBRICA ILO ILO MOQUEGUA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -927,7 +927,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>27850</t>
+          <t>2821</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -952,27 +952,27 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-17.641547</t>
+          <t>-17.64970628</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-71.339129</t>
+          <t>-71.3453818</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>CLINICA SAGRADO CORAZON</t>
+          <t>P.S. VARADERO</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>URBANIZACION URBANIZACION ADUANEROS L 02 Altura del ex-cine Ilo en la Av. Lino Urquieta, subiendo por el CEO Cesar Vallejo ILO ILO MOQUEGUA</t>
+          <t>OTROS NYLON SAN PEDRO F-3 NYLON SAN PEDRO F-3 ILO ILO MOQUEGUA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -989,7 +989,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>18616</t>
+          <t>2822</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1014,27 +1014,27 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-17.64434949</t>
+          <t>-17.65921341</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-71.34503948</t>
+          <t>-71.34710496</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>POLICLINICO SERVIMEDIQ</t>
+          <t>P.S. 18 DE MAYO</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>JR. ABTAO Nº 437 - 443 DISTRITO ILO PROVINCIA ILO DEPARTAMENTO MOQUEGUA</t>
+          <t>OTROS 18 DE MAYO  MZ. K LOTE 11   UPIS ALTO ILO 18 DE MAYO  MZ. K LOTE 11   UPIS ALTO ILO ILO ILO MOQUEGUA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1051,7 +1051,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>30209</t>
+          <t>28386</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1076,27 +1076,27 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-17.643273</t>
+          <t>-17.6914938</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-71.341157</t>
+          <t>-71.36762</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Centro Medico Especializado MMD 4M EIRL</t>
+          <t>AGRUPAMIENTO  DE COHETES ANTIAEREO "CRL JOSE GALVEZ"</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>CALLE Moquegua NUMERO 886 PISO 2 DISTRITO ILO PROVINCIA ILO DEPARTAMENTO MOQUEGUA</t>
+          <t>CARRETERA COSTANERA PUNTA COLES KILOMETRO 15 DISTRITO ILO PROVINCIA ILO DEPARTAMENTO MOQUEGUA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1113,7 +1113,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>29951</t>
+          <t>33157</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1138,22 +1138,22 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-17.65011675</t>
+          <t>-17.63351359</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-71.33163445</t>
+          <t>-71.33578218</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>POLICLINICO SERSIMED SEDE ILO</t>
+          <t>C. S. Mental Comunitario Dr. CA©sar Gallardo</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>URBANIZACION LUIS ERNESTO VALCARCEL NUMERO 53 PISO 1 MANZANA 53 LOTE 02 URBANIZACION LUIS ERNESTO VALCARCEL DISTRITO ILO PROVINCIA ILO DEPARTAMENTO MOQUEGUA</t>
+          <t>CALLE San MartA­n S/N Costado del Centro de Salud Miramar de Ilo ILO ILO MOQUEGUA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">

--- a/EstablecimientoSalud/excels/MOQUEGUA-ILO-ILO.xlsx
+++ b/EstablecimientoSalud/excels/MOQUEGUA-ILO-ILO.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Codigo_Unico</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -482,40 +482,35 @@
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Siniestros_fatales</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>180301</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MOQUEGUA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ILO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>ILO</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>2819</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>180301</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>MOQUEGUA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>ILO</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>ILO</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-17.65185454</t>
@@ -544,40 +539,35 @@
       <c r="K2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>180301</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>180301</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>MOQUEGUA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ILO</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ILO</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>23034</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>180301</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>MOQUEGUA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>ILO</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>ILO</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-17.65268394</t>
@@ -606,40 +596,35 @@
       <c r="K3" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>180301</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>180301</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MOQUEGUA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ILO</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ILO</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>34031</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>180301</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>MOQUEGUA</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>ILO</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>ILO</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-17.65242835</t>
@@ -668,40 +653,35 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>180301</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>180301</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>MOQUEGUA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ILO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ILO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>25870</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>180301</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>MOQUEGUA</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>ILO</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>ILO</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-17.64437606</t>
@@ -730,40 +710,35 @@
       <c r="K5" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>180301</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>180301</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>MOQUEGUA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ILO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ILO</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>2817</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>180301</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>MOQUEGUA</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>ILO</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>ILO</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-17.634884</t>
@@ -792,40 +767,35 @@
       <c r="K6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>180301</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>180301</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>MOQUEGUA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ILO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ILO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>12046</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>180301</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>MOQUEGUA</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>ILO</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>ILO</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-17.644121</t>
@@ -854,40 +824,35 @@
       <c r="K7" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>180301</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>180301</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MOQUEGUA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ILO</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ILO</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>7731</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>180301</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>MOQUEGUA</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>ILO</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>ILO</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-17.65531778</t>
@@ -916,40 +881,35 @@
       <c r="K8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>180301</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>180301</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>MOQUEGUA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ILO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ILO</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>2821</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>180301</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>MOQUEGUA</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>ILO</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>ILO</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-17.64970628</t>
@@ -978,40 +938,35 @@
       <c r="K9" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>180301</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>180301</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MOQUEGUA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ILO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ILO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>2822</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>180301</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>MOQUEGUA</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>ILO</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>ILO</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-17.65921341</t>
@@ -1040,40 +995,35 @@
       <c r="K10" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>180301</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>180301</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>MOQUEGUA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ILO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ILO</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>28386</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>180301</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>MOQUEGUA</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>ILO</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>ILO</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-17.6914938</t>
@@ -1102,40 +1052,35 @@
       <c r="K11" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>180301</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>180301</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>MOQUEGUA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ILO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ILO</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>33157</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>180301</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>MOQUEGUA</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>ILO</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>ILO</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-17.63351359</t>
@@ -1164,11 +1109,6 @@
       <c r="K12" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>180301</t>
         </is>
       </c>
     </row>

--- a/EstablecimientoSalud/excels/MOQUEGUA-ILO-ILO.xlsx
+++ b/EstablecimientoSalud/excels/MOQUEGUA-ILO-ILO.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Codigo_Unico</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
